--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260923.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>9.64%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.29%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.73%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.60%</t>
+          <t>4.62%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.04%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -887,44 +887,44 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>32,456,000</t>
+          <t>354,020,964</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>354,020,964</t>
+          <t>32,456,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>29,496,000</t>
+          <t>99,033,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>99,033,000</t>
+          <t>29,496,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -1166,24 +1166,24 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>191,053,000</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>191,053,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,103,710,962</t>
+          <t>10,175,607,904</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,113,700,829</t>
+          <t>7,144,446,629</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7,286,076</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
